--- a/sheets/조재수대금교본/검수/희망가풀이.xlsx
+++ b/sheets/조재수대금교본/검수/희망가풀이.xlsx
@@ -4191,55 +4191,52 @@
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林∼
-–ㄴ</t>
+–</t>
         </is>
       </c>
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ
-⊏</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ
-⊏</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="K3" s="22"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林∼
-–ㄴ</t>
+–</t>
         </is>
       </c>
       <c r="M3" s="22"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ
-⊏</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林∼
-–ㄴ</t>
+–</t>
         </is>
       </c>
       <c r="Q3" s="22"/>
@@ -4302,17 +4299,9 @@
         </is>
       </c>
       <c r="C6" s="22"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="D6" s="21"/>
       <c r="E6" s="22"/>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z∧</t>
-        </is>
-      </c>
+      <c r="F6" s="21"/>
       <c r="G6" s="22"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
@@ -4326,23 +4315,11 @@
         </is>
       </c>
       <c r="K6" s="22"/>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L6" s="21"/>
       <c r="M6" s="22"/>
-      <c r="N6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z∧</t>
-        </is>
-      </c>
+      <c r="N6" s="21"/>
       <c r="O6" s="22"/>
-      <c r="P6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="P6" s="21"/>
       <c r="Q6" s="22"/>
     </row>
     <row r="7" ht="90.2" customHeight="true">
@@ -4350,14 +4327,14 @@
       <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-–И</t>
+–</t>
         </is>
       </c>
       <c r="C7" s="23"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-∧汰潢</t>
+汰潢</t>
         </is>
       </c>
       <c r="E7" s="23"/>
@@ -4377,14 +4354,14 @@
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-–И</t>
+–</t>
         </is>
       </c>
       <c r="K7" s="23"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-∧汰潢</t>
+汰潢</t>
         </is>
       </c>
       <c r="M7" s="23"/>
@@ -4398,7 +4375,7 @@
       <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-∧汰潢</t>
+汰潢</t>
         </is>
       </c>
       <c r="Q7" s="23"/>
@@ -4414,22 +4391,20 @@
       <c r="C8" s="24"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰㳞⊏
+          <t xml:space="preserve">汰㳞
 △</t>
         </is>
       </c>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="G8" s="24"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-‹</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="I8" s="24"/>
@@ -4443,21 +4418,19 @@
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰㳞
-⊏
 △</t>
         </is>
       </c>
       <c r="M8" s="24"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="O8" s="24"/>
       <c r="P8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰㳞⊏
+          <t xml:space="preserve">汰㳞
 △</t>
         </is>
       </c>
@@ -4473,7 +4446,7 @@
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋∽</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="E9" s="22"/>
@@ -4483,11 +4456,7 @@
         </is>
       </c>
       <c r="G9" s="22"/>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">∧∽</t>
-        </is>
-      </c>
+      <c r="H9" s="21"/>
       <c r="I9" s="22"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
@@ -4497,7 +4466,7 @@
       <c r="K9" s="22"/>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋∽</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="M9" s="22"/>
@@ -4509,7 +4478,7 @@
       <c r="O9" s="22"/>
       <c r="P9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋∽</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="Q9" s="22"/>
@@ -4521,21 +4490,20 @@
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-∧湳</t>
+湳</t>
         </is>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-–И</t>
+–</t>
         </is>
       </c>
       <c r="G10" s="23"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I10" s="23"/>
@@ -4543,8 +4511,7 @@
       <c r="K10" s="23"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M10" s="23"/>
@@ -4556,8 +4523,7 @@
       <c r="O10" s="23"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q10" s="23"/>
@@ -4568,7 +4534,7 @@
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋㳞⊏
+          <t xml:space="preserve">淋㳞
 –汰</t>
         </is>
       </c>
@@ -4576,14 +4542,13 @@
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林南
-–ﾉ</t>
+–</t>
         </is>
       </c>
       <c r="G11" s="24"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-‹</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="I11" s="24"/>
@@ -4592,8 +4557,7 @@
       <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-⊏
-–⌝∽</t>
+–</t>
         </is>
       </c>
       <c r="M11" s="24"/>
@@ -4607,8 +4571,7 @@
       <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-⊏
-–⌝∽</t>
+–</t>
         </is>
       </c>
       <c r="Q11" s="24"/>
@@ -4625,7 +4588,7 @@
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㅋ</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -4645,7 +4608,7 @@
       <c r="M12" s="22"/>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㅋ∼</t>
+          <t xml:space="preserve">林∼</t>
         </is>
       </c>
       <c r="O12" s="22"/>
@@ -4663,7 +4626,7 @@
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-∧汰潢</t>
+汰潢</t>
         </is>
       </c>
       <c r="E13" s="23"/>
@@ -4694,22 +4657,16 @@
       <c r="C14" s="24"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳淋
-湳
-‹</t>
+湳</t>
         </is>
       </c>
       <c r="I14" s="24"/>
@@ -4722,21 +4679,15 @@
       <c r="K14" s="24"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="M14" s="24"/>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N14" s="21"/>
       <c r="O14" s="24"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="Q14" s="24"/>
@@ -4780,28 +4731,26 @@
       <c r="J17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳淋
-㳞
-⊏</t>
+㳞</t>
         </is>
       </c>
       <c r="K17" s="22"/>
       <c r="L17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林∼
-–ㄴ</t>
+–</t>
         </is>
       </c>
       <c r="M17" s="22"/>
       <c r="N17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ
-⊏</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="O17" s="22"/>
       <c r="P17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="Q17" s="22"/>
@@ -4839,11 +4788,7 @@
       <c r="G19" s="24"/>
       <c r="H19" s="21"/>
       <c r="I19" s="24"/>
-      <c r="J19" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J19" s="21"/>
       <c r="K19" s="24"/>
       <c r="L19" s="21"/>
       <c r="M19" s="24"/>
@@ -4868,17 +4813,9 @@
         </is>
       </c>
       <c r="K20" s="22"/>
-      <c r="L20" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L20" s="21"/>
       <c r="M20" s="22"/>
-      <c r="N20" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="N20" s="21"/>
       <c r="O20" s="22"/>
       <c r="P20" s="21"/>
       <c r="Q20" s="22"/>
@@ -4903,7 +4840,7 @@
       <c r="L21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-∧汰潢</t>
+汰潢</t>
         </is>
       </c>
       <c r="M21" s="23"/>
@@ -4930,23 +4867,20 @@
       <c r="J22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-湳
-‹</t>
+湳</t>
         </is>
       </c>
       <c r="K22" s="24"/>
       <c r="L22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰㳞
-⊏
 △</t>
         </is>
       </c>
       <c r="M22" s="24"/>
       <c r="N22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="O22" s="24"/>
@@ -4963,29 +4897,24 @@
       <c r="G23" s="22"/>
       <c r="H23" s="21"/>
       <c r="I23" s="22"/>
-      <c r="J23" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">∧∽</t>
-        </is>
-      </c>
+      <c r="J23" s="21"/>
       <c r="K23" s="22"/>
       <c r="L23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋∽</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="M23" s="22"/>
       <c r="N23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-⊏
 –汰</t>
         </is>
       </c>
       <c r="O23" s="22"/>
       <c r="P23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∧湳
+          <t xml:space="preserve">湳
 淋</t>
         </is>
       </c>
@@ -5005,8 +4934,7 @@
       <c r="K24" s="23"/>
       <c r="L24" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-И</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M24" s="23"/>
@@ -5035,17 +4963,11 @@
       <c r="L25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-⊏
-–⌝∽</t>
+–</t>
         </is>
       </c>
       <c r="M25" s="24"/>
-      <c r="N25" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="N25" s="21"/>
       <c r="O25" s="24"/>
       <c r="P25" s="21"/>
       <c r="Q25" s="24"/>
@@ -5112,23 +5034,14 @@
         </is>
       </c>
       <c r="K28" s="24"/>
-      <c r="L28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L28" s="21"/>
       <c r="M28" s="24"/>
-      <c r="N28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N28" s="21"/>
       <c r="O28" s="24"/>
       <c r="P28" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳淋
-湳
-‹</t>
+湳</t>
         </is>
       </c>
       <c r="Q28" s="24"/>

--- a/sheets/조재수대금교본/검수/희망가풀이.xlsx
+++ b/sheets/조재수대금교본/검수/희망가풀이.xlsx
@@ -4191,52 +4191,55 @@
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ</t>
         </is>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林∼
-–</t>
+–ㄴ</t>
         </is>
       </c>
       <c r="E3" s="22"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ
+⊏</t>
         </is>
       </c>
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ</t>
         </is>
       </c>
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ
+⊏</t>
         </is>
       </c>
       <c r="K3" s="22"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林∼
-–</t>
+–ㄴ</t>
         </is>
       </c>
       <c r="M3" s="22"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ
+⊏</t>
         </is>
       </c>
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林∼
-–</t>
+–ㄴ</t>
         </is>
       </c>
       <c r="Q3" s="22"/>
@@ -4299,9 +4302,17 @@
         </is>
       </c>
       <c r="C6" s="22"/>
-      <c r="D6" s="21"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="E6" s="22"/>
-      <c r="F6" s="21"/>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z∧</t>
+        </is>
+      </c>
       <c r="G6" s="22"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
@@ -4315,11 +4326,23 @@
         </is>
       </c>
       <c r="K6" s="22"/>
-      <c r="L6" s="21"/>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M6" s="22"/>
-      <c r="N6" s="21"/>
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z∧</t>
+        </is>
+      </c>
       <c r="O6" s="22"/>
-      <c r="P6" s="21"/>
+      <c r="P6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="Q6" s="22"/>
     </row>
     <row r="7" ht="90.2" customHeight="true">
@@ -4327,14 +4350,14 @@
       <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-–</t>
+–И</t>
         </is>
       </c>
       <c r="C7" s="23"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰潢</t>
+∧汰潢</t>
         </is>
       </c>
       <c r="E7" s="23"/>
@@ -4354,14 +4377,14 @@
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-–</t>
+–И</t>
         </is>
       </c>
       <c r="K7" s="23"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰潢</t>
+∧汰潢</t>
         </is>
       </c>
       <c r="M7" s="23"/>
@@ -4375,7 +4398,7 @@
       <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰潢</t>
+∧汰潢</t>
         </is>
       </c>
       <c r="Q7" s="23"/>
@@ -4391,7 +4414,7 @@
       <c r="C8" s="24"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰㳞
+          <t xml:space="preserve">汰㳞⊏
 △</t>
         </is>
       </c>
@@ -4418,6 +4441,7 @@
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰㳞
+⊏
 △</t>
         </is>
       </c>
@@ -4430,7 +4454,7 @@
       <c r="O8" s="24"/>
       <c r="P8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰㳞
+          <t xml:space="preserve">汰㳞⊏
 △</t>
         </is>
       </c>
@@ -4446,7 +4470,7 @@
       <c r="C9" s="22"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋∽</t>
         </is>
       </c>
       <c r="E9" s="22"/>
@@ -4456,7 +4480,11 @@
         </is>
       </c>
       <c r="G9" s="22"/>
-      <c r="H9" s="21"/>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">∧∽</t>
+        </is>
+      </c>
       <c r="I9" s="22"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
@@ -4466,7 +4494,7 @@
       <c r="K9" s="22"/>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋∽</t>
         </is>
       </c>
       <c r="M9" s="22"/>
@@ -4478,7 +4506,7 @@
       <c r="O9" s="22"/>
       <c r="P9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋∽</t>
         </is>
       </c>
       <c r="Q9" s="22"/>
@@ -4490,20 +4518,21 @@
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-湳</t>
+∧湳</t>
         </is>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-–</t>
+–И</t>
         </is>
       </c>
       <c r="G10" s="23"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="I10" s="23"/>
@@ -4511,7 +4540,8 @@
       <c r="K10" s="23"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="M10" s="23"/>
@@ -4523,7 +4553,8 @@
       <c r="O10" s="23"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="Q10" s="23"/>
@@ -4534,7 +4565,7 @@
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋㳞
+          <t xml:space="preserve">淋㳞⊏
 –汰</t>
         </is>
       </c>
@@ -4542,7 +4573,7 @@
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林南
-–</t>
+–ﾉ</t>
         </is>
       </c>
       <c r="G11" s="24"/>
@@ -4557,7 +4588,8 @@
       <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-–</t>
+⊏
+–⌝∽</t>
         </is>
       </c>
       <c r="M11" s="24"/>
@@ -4571,7 +4603,8 @@
       <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-–</t>
+⊏
+–⌝∽</t>
         </is>
       </c>
       <c r="Q11" s="24"/>
@@ -4588,7 +4621,7 @@
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">林ㅋ</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -4608,7 +4641,7 @@
       <c r="M12" s="22"/>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林∼</t>
+          <t xml:space="preserve">林ㅋ∼</t>
         </is>
       </c>
       <c r="O12" s="22"/>
@@ -4626,7 +4659,7 @@
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰潢</t>
+∧汰潢</t>
         </is>
       </c>
       <c r="E13" s="23"/>
@@ -4731,26 +4764,28 @@
       <c r="J17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳淋
-㳞</t>
+㳞
+⊏</t>
         </is>
       </c>
       <c r="K17" s="22"/>
       <c r="L17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林∼
-–</t>
+–ㄴ</t>
         </is>
       </c>
       <c r="M17" s="22"/>
       <c r="N17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㳞ㄱ
+⊏</t>
         </is>
       </c>
       <c r="O17" s="22"/>
       <c r="P17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ</t>
         </is>
       </c>
       <c r="Q17" s="22"/>
@@ -4813,9 +4848,17 @@
         </is>
       </c>
       <c r="K20" s="22"/>
-      <c r="L20" s="21"/>
+      <c r="L20" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M20" s="22"/>
-      <c r="N20" s="21"/>
+      <c r="N20" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="O20" s="22"/>
       <c r="P20" s="21"/>
       <c r="Q20" s="22"/>
@@ -4840,7 +4883,7 @@
       <c r="L21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰潢</t>
+∧汰潢</t>
         </is>
       </c>
       <c r="M21" s="23"/>
@@ -4874,6 +4917,7 @@
       <c r="L22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰㳞
+⊏
 △</t>
         </is>
       </c>
@@ -4897,24 +4941,29 @@
       <c r="G23" s="22"/>
       <c r="H23" s="21"/>
       <c r="I23" s="22"/>
-      <c r="J23" s="21"/>
+      <c r="J23" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">∧∽</t>
+        </is>
+      </c>
       <c r="K23" s="22"/>
       <c r="L23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋∽</t>
         </is>
       </c>
       <c r="M23" s="22"/>
       <c r="N23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
+⊏
 –汰</t>
         </is>
       </c>
       <c r="O23" s="22"/>
       <c r="P23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
+          <t xml:space="preserve">∧湳
 淋</t>
         </is>
       </c>
@@ -4934,7 +4983,8 @@
       <c r="K24" s="23"/>
       <c r="L24" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+И</t>
         </is>
       </c>
       <c r="M24" s="23"/>
@@ -4963,11 +5013,16 @@
       <c r="L25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-–</t>
+⊏
+–⌝∽</t>
         </is>
       </c>
       <c r="M25" s="24"/>
-      <c r="N25" s="21"/>
+      <c r="N25" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="O25" s="24"/>
       <c r="P25" s="21"/>
       <c r="Q25" s="24"/>

--- a/sheets/조재수대금교본/검수/희망가풀이.xlsx
+++ b/sheets/조재수대금교본/검수/희망가풀이.xlsx
@@ -4143,28 +4143,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="13.46" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60.61" customHeight="true">
+    <row r="2" ht="74.07" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="90.2" customHeight="true">
+    <row r="3" ht="110.36" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="90.2" customHeight="true">
+    <row r="4" ht="110.36" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="90.2" customHeight="true">
+    <row r="5" ht="110.36" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
@@ -4294,7 +4294,7 @@
       <c r="P5" s="21"/>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="90.2" customHeight="true">
+    <row r="6" ht="110.36" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="90.2" customHeight="true">
+    <row r="7" ht="110.36" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="90.2" customHeight="true">
+    <row r="8" ht="110.36" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" ht="90.2" customHeight="true">
+    <row r="9" ht="110.36" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="90.2" customHeight="true">
+    <row r="10" ht="110.36" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="90.2" customHeight="true">
+    <row r="11" ht="110.36" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="90.2" customHeight="true">
+    <row r="12" ht="110.36" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="90.2" customHeight="true">
+    <row r="13" ht="110.36" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -4680,7 +4680,7 @@
       <c r="P13" s="21"/>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="90.2" customHeight="true">
+    <row r="14" ht="110.36" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
     <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="60.61" customHeight="true">
+    <row r="16" ht="74.07" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
       <c r="P16" s="20"/>
       <c r="Q16" s="20"/>
     </row>
-    <row r="17" ht="90.2" customHeight="true">
+    <row r="17" ht="110.36" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="Q17" s="22"/>
     </row>
-    <row r="18" ht="90.2" customHeight="true">
+    <row r="18" ht="110.36" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="23"/>
@@ -4813,7 +4813,7 @@
       <c r="P18" s="21"/>
       <c r="Q18" s="23"/>
     </row>
-    <row r="19" ht="90.2" customHeight="true">
+    <row r="19" ht="110.36" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="24"/>
@@ -4832,7 +4832,7 @@
       <c r="P19" s="21"/>
       <c r="Q19" s="24"/>
     </row>
-    <row r="20" ht="90.2" customHeight="true">
+    <row r="20" ht="110.36" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="22"/>
@@ -4863,7 +4863,7 @@
       <c r="P20" s="21"/>
       <c r="Q20" s="22"/>
     </row>
-    <row r="21" ht="90.2" customHeight="true">
+    <row r="21" ht="110.36" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="23"/>
@@ -4897,7 +4897,7 @@
       <c r="P21" s="21"/>
       <c r="Q21" s="23"/>
     </row>
-    <row r="22" ht="90.2" customHeight="true">
+    <row r="22" ht="110.36" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="24"/>
@@ -4931,7 +4931,7 @@
       <c r="P22" s="21"/>
       <c r="Q22" s="24"/>
     </row>
-    <row r="23" ht="90.2" customHeight="true">
+    <row r="23" ht="110.36" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="Q23" s="22"/>
     </row>
-    <row r="24" ht="90.2" customHeight="true">
+    <row r="24" ht="110.36" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -4998,7 +4998,7 @@
       <c r="P24" s="21"/>
       <c r="Q24" s="23"/>
     </row>
-    <row r="25" ht="90.2" customHeight="true">
+    <row r="25" ht="110.36" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="24"/>
@@ -5027,7 +5027,7 @@
       <c r="P25" s="21"/>
       <c r="Q25" s="24"/>
     </row>
-    <row r="26" ht="90.2" customHeight="true">
+    <row r="26" ht="110.36" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -5054,7 +5054,7 @@
       <c r="P26" s="21"/>
       <c r="Q26" s="22"/>
     </row>
-    <row r="27" ht="90.2" customHeight="true">
+    <row r="27" ht="110.36" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -5073,7 +5073,7 @@
       <c r="P27" s="21"/>
       <c r="Q27" s="23"/>
     </row>
-    <row r="28" ht="90.2" customHeight="true">
+    <row r="28" ht="110.36" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21"/>
       <c r="C28" s="24"/>
@@ -5108,7 +5108,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="54"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="14" max="16383" man="1"/>
   </rowBreaks>
